--- a/planilha.xlsx
+++ b/planilha.xlsx
@@ -15,11 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instituições" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Registros'!$A$1:$U$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sítios'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Registros'!$A$1:$U$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sítios'!$A$1:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Períodos'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Biozonas'!$A$1:$E$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Instituições'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Instituições'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Paleo-RS — versão 2026.09.1 (2026-09-16)</t>
+          <t>Paleo-RS — versão 2026.09.2 (2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1345,8 +1345,780 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pampaphoneus biccai Cisneros et al., 2012</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vertebrado — sinapsídeo (Therapsida, Dinocephalia)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Permiano Médio (Guadalupiano)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ca. 265 Ma</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fm. Rio do Rasto / Membro Morro Pelado</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Supersequência Gondwana I</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>São Gabriel</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Fazenda Boqueirão, distrito de Catuçaba, São Gabriel, RS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Fazenda Boqueirão</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>-30.0022</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-54.0858</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>UFRGS PV386P (holótipo); UNIPAMPA 759 (segundo crânio)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Laboratório de Paleovertebrados, UFRGS, Porto Alegre; UNIPAMPA, São Gabriel</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>UFRGS; UNIPAMPA</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Cisneros, J.C. et al. (2012) — PNAS 109(5):1584-1588</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Artigo em periódico</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>10.1073/pnas.1115975109</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Maior predador terrestre conhecido do Permiano brasileiro e o primeiro dinocéfalo descrito fora da Rússia e da África do Sul — evidência direta de dispersão de tetrápodes pela Pangeia. Coordenada publicada na descrição original (S 30°00'08"; W 54°05'09"). Um segundo crânio quase completo, UNIPAMPA 759, foi descrito por Costa Santos et al. (2023) no Zoological Journal of the Linnean Society 199(4):1034, do mesmo afloramento.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>CISNEROS, J. C. et al. Carnivorous dinocephalian from the Middle Permian of Brazil and tetrapod dispersal in Pangaea. PNAS, v. 109, n. 5, p. 1584-1588, 2012.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rastodon procurvidens Boos et al., 2016</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Vertebrado — sinapsídeo (Therapsida, Dicynodontia)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Permiano Médio (Guadalupiano)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ca. 265 Ma</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fm. Rio do Rasto / Membro Morro Pelado</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Supersequência Gondwana I</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>São Gabriel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Fazenda Boqueirão, São Gabriel, RS</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Fazenda Boqueirão</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-30.0022</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-54.0858</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>UNIPAMPA 317 (holótipo; também citado como UNIPAMPA PV317P)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Laboratório de Paleobiologia, UNIPAMPA, São Gabriel</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>UNIPAMPA; UFRGS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Boos, A.D.S.; Kammerer, C.F.; Schultz, C.L.; Soares, M.B.; Ilha, A.L.R. (2016)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Artigo em periódico</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Único dicinodonte permiano da América do Sul conhecido por crânio completo. Presas pequenas e curvadas para a frente, caráter único no grupo. Coletado no mesmo afloramento que Pampaphoneus biccai e Konzhukovia sangabrielensis. O DOI da descrição original de 2016 não foi confirmado nas fontes consultadas e não foi deduzido; a fonte registrada é o estudo endocraniano de Simão-Oliveira et al. (2020), Journal of Anatomy, que descreve o mesmo holótipo. Reinterpretado como Kingoriidae em revisão de 2025 — ver a ficha antes de citar a posição filogenética.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>BOOS, A. D. S. et al. A new dicynodont (Therapsida: Anomodontia) from the Permian of southern Brazil and its implications for bidentalian origins. 2016.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Konzhukovia sangabrielensis Pacheco et al., 2017</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vertebrado — anfíbio (Temnospondyli, Archegosauriformes)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Permiano Médio (Guadalupiano)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ca. 265 Ma</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fm. Rio do Rasto / Membro Morro Pelado</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Supersequência Gondwana I</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>São Gabriel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Fazenda Boqueirão, São Gabriel, RS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Fazenda Boqueirão</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-30.0022</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-54.0858</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>UNIPAMPA; UFRGS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Pacheco, C.P. et al. (2017), citado em Kammerer (2021) e em Costa Santos et al. (2023)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Citação em revisão</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>REGISTRO FRÁGIL — não verificado na publicação original. O táxon é citado em duas revisões consultadas como tendo holótipo do mesmo afloramento de Pampaphoneus e Rastodon, mas nem o número de tombo nem a instituição de guarda foram confirmados. Primeiro Konzhukovia fora da Rússia, o que sustenta a mesma hipótese de conexão faunística da Pangeia. Abrir a descrição original de 2017 e completar tombo, guarda e DOI antes de citar.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Riograndia guaibensis Bonaparte, Ferigolo &amp; Ribeiro, 2001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Vertebrado — cinodonte (Probainognathia, Prozostrodontia)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Triássico Superior (Noriano)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ca. 225,42 ± 0,37 Ma</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fm. Caturrita / Sequência Candelária</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Supersequência Santa Maria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Candelária</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Afloramento Sesmaria do Pinhal 1, Candelária, RS</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sesmaria do Pinhal 1</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>-29.6667</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-52.7833</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>MCN-PV 2264 (holótipo); UFRGS-PV-596-T e UFRGS-PV-788-T (referidos)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Museu de Ciências Naturais, Porto Alegre; UFRGS, Porto Alegre</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>MCN; UFRGS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Bonaparte, J.F.; Ferigolo, J.; Ribeiro, A.M. (2001); redescrição em Fonseca et al. (2025), The Anatomical Record</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Artigo em periódico</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>10.1002/ar.25540</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dá nome à Zona de Assembleia de Riograndia, o intervalo noriano que contém a fauna mais próxima da origem dos mamíferos no Brasil. Candelária é referência mundial nessa linhagem. Coordenada regional: as fontes consultadas nomeiam o afloramento mas não publicam coordenada — usada a sede municipal de Candelária. Corrigir quando houver coordenada publicada. O DOI registrado é o da redescrição do canal maxilar, em acesso fechado.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>BONAPARTE, J. F.; FERIGOLO, J.; RIBEIRO, A. M. A primitive Late Triassic 'ictidosaur' from Rio Grande do Sul, Brazil. Palaeontology, v. 44, n. 4, p. 623-635, 2001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brasilodon quadrangularis Bonaparte et al., 2003</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Vertebrado — cinodonte (Probainognathia, Brasilodontidae)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Triássico Superior (Noriano)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ca. 225,42 ± 0,37 Ma</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fm. Caturrita / Sequência Candelária</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Supersequência Santa Maria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Faxinal do Soturno</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sítio Linha São Luiz, Faxinal do Soturno, RS</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Linha São Luiz</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>-29.5789</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-53.4436</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UFRGS-PV-0611-T (holótipo); UFRGS-PV-0628-T, 0765-T (referidos)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Departamento de Paleontologia e Estratigrafia, UFRGS, Porto Alegre</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>UFRGS; MCN</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Bonaparte, J.F. et al. (2003); pós-crânio em Bonaparte et al. (2019), PLOS ONE 14(5):e0216672</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Artigo em periódico</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pone.0216672</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Cinodonte não-mamaliaforme com traços de mamaliaforme no pós-crânio — um dos táxons mais citados na discussão sobre onde termina o cinodonte e começa o mamífero. Espécimes conhecidos de dois sítios, Linha São Luiz (Faxinal do Soturno) e Sesmaria do Pinhal (Candelária); este registro cobre o de Faxinal do Soturno. Coordenada regional: a publicação mapeia o sítio mas não publica coordenada — usada a sede municipal.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>BONAPARTE, J. F. et al. The postcranial anatomy of Brasilodon quadrangularis and the acquisition of mammaliaform traits among non-mammaliaform cynodonts. PLOS ONE, v. 14, n. 5, e0216672, 2019.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Guaibasaurus candelariensis Bonaparte, Ferigolo &amp; Ribeiro, 1999</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Vertebrado — dinossauro (Saurischia basal)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Triássico Superior (Noriano)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ca. 225 Ma</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fm. Caturrita / Sequência Candelária</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Supersequência Santa Maria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Faxinal do Soturno</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sítio Linha São Luiz, Faxinal do Soturno, RS</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Linha São Luiz</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>-29.5789</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-53.4436</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>MCN; UFRGS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Bonaparte, J.F.; Ferigolo, J.; Ribeiro, A.M. (1999), citado em Soares, Schultz &amp; Horn (2011), An. Acad. Bras. Ciênc. 83(1)</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Citação em revisão</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>REGISTRO FRÁGIL — este registro cobre o espécime de Faxinal do Soturno, citado em revisão, não o holótipo. Homonímia a documentar: o epíteto candelariensis vem de Candelária, município do holótipo, mas o material aqui catalogado é de Faxinal do Soturno, a cerca de 60 km. Tombo, guarda e coordenada não confirmados. Verificar a descrição original de 1999 e o artigo de 2007 sobre o novo espécime antes de citar.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Soturnia caliodon Cisneros &amp; Schultz, 2003</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Vertebrado — parareptil (Procolophonidae)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Triássico Superior (Noriano)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ca. 225 Ma</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fm. Caturrita / Sequência Candelária</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Supersequência Santa Maria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Faxinal do Soturno</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sítio Linha São Luiz, Faxinal do Soturno, RS</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Linha São Luiz</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>-29.5789</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-53.4436</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>UFRGS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Cisneros, J.C.; Schultz, C.L. (2003), citado em Soares, Schultz &amp; Horn (2011), An. Acad. Bras. Ciênc. 83(1)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Citação em revisão</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>REGISTRO FRÁGIL — procolofonídeo da mesma fauna de Riograndia e Brasilodon, listado em revisão. Tombo, guarda e coordenada não confirmados na fonte consultada. Abrir a descrição original antes de citar.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Clevosaurus brasiliensis Bonaparte &amp; Sues, 2006</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vertebrado — lepidossauro (Rhynchocephalia, Clevosauridae)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Triássico Superior (Noriano)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ca. 225 Ma</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fm. Caturrita / Sequência Candelária</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná — Supersequência Santa Maria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Faxinal do Soturno</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sítio Linha São Luiz, Faxinal do Soturno, RS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Linha São Luiz</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>-29.5789</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-53.4436</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>UFRGS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Bonaparte, J.F.; Sues, H.-D. (2006), citado em Soares, Schultz &amp; Horn (2011), An. Acad. Bras. Ciênc. 83(1)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Citação em revisão</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>REGISTRO FRÁGIL — parente triássico do tuatara, na mesma fauna de Faxinal do Soturno. Um dos registros mais antigos do clado clevosaurídeo segundo a revisão consultada. Tombo, guarda e coordenada não confirmados. Abrir a descrição original antes de citar.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U8"/>
+  <autoFilter ref="A1:U16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1357,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1530,8 +2302,86 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fazenda Boqueirão</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>São Gabriel</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-30.0022</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-54.0858</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>publicada</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sesmaria do Pinhal 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Candelária</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-29.6667</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-52.7833</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Linha São Luiz</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Faxinal do Soturno</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-29.5789</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-53.4436</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1675,7 +2525,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1704,7 +2554,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -2013,7 +2863,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2028,7 +2878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2284,32 +3134,113 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>UFRGS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio Grande do Sul — Laboratório de Paleovertebrados</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Porto Alegre, RS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.ufrgs.br/paleovertebrados/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Série UFRGS-PV, uma das maiores coleções de vertebrados fósseis do Brasil; referência em cinodontes triássicos e terápsidas permianos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UNIPAMPA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Pampa — Laboratório de Paleobiologia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>São Gabriel, RS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://unipampa.edu.br</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tetrápodes permianos da Fm. Rio do Rasto; guarda os holótipos de Rastodon procurvidens e o segundo crânio de Pampaphoneus biccai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MCN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Museu de Ciências Naturais (ex-Fundação Zoobotânica do RS)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Porto Alegre, RS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.sema.rs.gov.br</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Série MCN-PV; guarda os holótipos de Riograndia guaibensis e Guaibasaurus candelariensis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>PUCRS</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Pontifícia Universidade Católica do Rio Grande do Sul</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Porto Alegre, RS</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.pucrs.br</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Laboratório de Sedimentologia e Petrologia; microtomografia de fósseis.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/planilha.xlsx
+++ b/planilha.xlsx
@@ -450,7 +450,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Paleo-RS — versão 2026.09.2 (2026-09-17)</t>
+          <t>Paleo-RS — versão 2026.09.3 (2026-09-17)</t>
         </is>
       </c>
     </row>
